--- a/public/modele-questions.xlsx
+++ b/public/modele-questions.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">Zone</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palier</t>
   </si>
   <si>
     <t xml:space="preserve">Quelle est la devise des scouts ?</t>
@@ -116,6 +119,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -145,6 +149,9 @@
       </c>
       <c r="I1" t="s" s="1">
         <v>8</v>
+      </c>
+      <c r="J1" t="s" s="1">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -163,6 +170,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -193,31 +201,34 @@
       <c r="I1" t="s" s="1">
         <v>8</v>
       </c>
+      <c r="J1" t="s" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
